--- a/data/trans_orig/IP07KS_C05_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C05_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3049</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6700</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4168</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7373</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8740</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4554</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12385</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>52,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3149</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6360</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25,38%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8692</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>56,64%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3074</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>44,26%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5090</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8505</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>41,03%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>68,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5334</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4679</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4699</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4558</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5464</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4138</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4690</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,74 +1402,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>91148</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76979</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>111653</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>42848</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21331</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55826</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>94805</t>
+          <t>44637</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77975</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116339</t>
+          <t>54586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>25,08%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>38,47%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>57,39%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>158</t>
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>137653</t>
+          <t>135785</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106675</t>
+          <t>117719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161498</t>
+          <t>157925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89524</t>
+          <t>82373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71036</t>
+          <t>65073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119940</t>
+          <t>96621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81103</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63328</t>
+          <t>59013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97450</t>
+          <t>79550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>170627</t>
+          <t>151842</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147122</t>
+          <t>132171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>213071</t>
+          <t>170542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16614</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10234</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26619</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>19067</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9533</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26978</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>20422</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>28875</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>37036</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46711</t>
+          <t>47823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8148</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6564</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13015</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17094</t>
+          <t>18135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6704</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13721</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2941</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7278</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3266</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16096</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>158546</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>158546</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>158546</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>141879</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>141879</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>141879</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>361246</t>
+          <t>342212</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>361246</t>
+          <t>342212</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>361246</t>
+          <t>342212</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23668</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17108</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30464</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17652</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12687</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22936</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>18253</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>23618</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41419</t>
+          <t>41922</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>33396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49857</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18459</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12812</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24518</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,26%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>17734</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>12442</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22707</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>45,76%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>37620</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28080</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43615</t>
+          <t>46445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4587</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1511</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3654</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4414</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1478</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10043</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3574</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7866</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3970</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8755</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>117866</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>101462</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>137781</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>37,56%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>51,01%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>64668</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>40955</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>79839</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>121557</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103624</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143032</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>186225</t>
+          <t>185184</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155270</t>
+          <t>164115</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214870</t>
+          <t>209276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>109573</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>93460</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>125611</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>46,51%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>110406</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>91211</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>144134</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>52,65%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,49%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>108065</t>
+          <t>91760</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>89311</t>
+          <t>79339</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126741</t>
+          <t>103427</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>218472</t>
+          <t>201333</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>192521</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261467</t>
+          <t>220995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22403</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14945</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>33440</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>26242</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>17308</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>36855</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31940</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>48017</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>39370</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9034</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>17382</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>7154</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>13524</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>11225</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6064</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>19476</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4400</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>11834</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>20713</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
